--- a/Assets/Power Rankings.xlsx
+++ b/Assets/Power Rankings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50e9598adf3d07f8/Documents/CDP App/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_0158F9881C49057749A4C2932F71AE9D500C120F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A097F811-8D38-4A67-AC10-A7018991EF9A}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_0158F9881C49057749A4C2932F71AE9D500C120F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAFB0C1A-B298-41D2-9D4B-2DFDB4827085}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,6 +255,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -333,34 +336,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -377,10 +388,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,792 +595,792 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="8">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="9">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="9">
         <v>1</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="15">
         <f t="shared" ref="G2:G33" si="0">AVERAGE(C2:F2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="10">
         <v>2</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="11">
         <v>2</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="12">
         <v>3</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="10">
         <v>2</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="15">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="7">
         <v>3</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="12">
         <v>4</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="12">
         <v>5</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="7">
         <v>4</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="15">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="7">
         <v>7</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="12">
         <v>3</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="12">
         <v>2</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="7">
         <v>5</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="15">
         <f t="shared" si="0"/>
         <v>4.25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="7">
         <v>9</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="12">
         <v>6</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="12">
         <v>4</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="7">
         <v>6</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="15">
         <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="7">
         <v>5</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="12">
         <v>8</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="12">
         <v>7</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="7">
         <v>8</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="13">
         <v>11</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="12">
         <v>9</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="12">
         <v>8</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="13">
         <v>3</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>7.75</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="7">
         <v>8</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="14">
         <v>5</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="12">
         <v>6</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="13">
         <v>14</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="15">
         <f t="shared" si="0"/>
         <v>8.25</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="13">
         <v>4</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="14">
         <v>13</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="12">
         <v>10</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="7">
         <v>12</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="15">
         <f t="shared" si="0"/>
         <v>9.75</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="13">
         <v>6</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="12">
         <v>11</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="12">
         <v>12</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="13">
         <v>15</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="7">
         <v>14</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="12">
         <v>10</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="12">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="7">
         <v>13</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="15">
         <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="7">
         <v>16</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="12">
         <v>15</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="12">
         <v>11</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="7">
         <v>9</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="15">
         <f t="shared" si="0"/>
         <v>12.75</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="7">
         <v>10</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="12">
         <v>14</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="12">
         <v>14</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="7">
         <v>16</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="15">
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="7">
         <v>13</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="12">
         <v>19</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="12">
         <v>15</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="7">
         <v>10</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="15">
         <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="7">
         <v>12</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="14">
         <v>7</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="12">
         <v>19</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="13">
         <v>22</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="15">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="7">
         <v>17</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="12">
         <v>12</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="12">
         <v>13</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="7">
         <v>19</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="15">
         <f t="shared" si="0"/>
         <v>15.25</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="7">
         <v>20</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="12">
         <v>18</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="12">
         <v>17</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="7">
         <v>11</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="15">
         <f t="shared" si="0"/>
         <v>16.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="7">
         <v>19</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="12">
         <v>20</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="14">
         <v>20</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="13">
         <v>7</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="15">
         <f t="shared" si="0"/>
         <v>16.5</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="10">
         <v>18</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="12">
         <v>17</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="11">
         <v>18</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="10">
         <v>18</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="15">
         <f t="shared" si="0"/>
         <v>17.75</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="7">
         <v>21</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="11">
         <v>16</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="11">
         <v>16</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="10">
         <v>25</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="15">
         <f t="shared" si="0"/>
         <v>19.5</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="7">
         <v>15</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="12">
         <v>24</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="12">
         <v>21</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="7">
         <v>20</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="15">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="7">
         <v>24</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="12">
         <v>21</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="12">
         <v>24</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="7">
         <v>21</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="15">
         <f t="shared" si="0"/>
         <v>22.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="7">
         <v>25</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="12">
         <v>23</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="12">
         <v>27</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="7">
         <v>17</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="15">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="7">
         <v>22</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="12">
         <v>25</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="12">
         <v>28</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="7">
         <v>27</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="15">
         <f t="shared" si="0"/>
         <v>25.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="7">
         <v>27</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="12">
         <v>27</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="12">
         <v>22</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="7">
         <v>26</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="15">
         <f t="shared" si="0"/>
         <v>25.5</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="7">
         <v>28</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="12">
         <v>22</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="12">
         <v>25</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="7">
         <v>29</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="15">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="7">
         <v>23</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="12">
         <v>28</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="12">
         <v>30</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="7">
         <v>23</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="15">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="7">
         <v>26</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="12">
         <v>26</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="12">
         <v>23</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="7">
         <v>31</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="15">
         <f t="shared" si="0"/>
         <v>26.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="7">
         <v>29</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="12">
         <v>29</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="12">
         <v>26</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="7">
         <v>30</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="15">
         <f t="shared" si="0"/>
         <v>28.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="7">
         <v>30</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="12">
         <v>31</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="12">
         <v>29</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="7">
         <v>24</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="15">
         <f t="shared" si="0"/>
         <v>28.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="7">
         <v>31</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="12">
         <v>30</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="12">
         <v>31</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="7">
         <v>28</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="15">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="8">
         <v>32</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="9">
         <v>32</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="9">
         <v>32</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="8">
         <v>32</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="15">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
